--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -11,8 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Концерты" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Направления" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Номера" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Таймкоды" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Люди" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Люди" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +38,7 @@
       <color rgb="001A0F05"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -49,11 +48,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FF8B36"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,7 +63,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -79,7 +73,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -227,21 +220,6 @@
 </file>
 
 <file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Каталог</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Время по записи концерта целиком, как на плеере: ч:мм:сс. Должно попадать между началом и концом номера.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Каталог</author>
@@ -545,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -609,63 +587,56 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4. Лист «Таймкоды»: метки внутри номера. Время — по видео концерта целиком, как на плеере.</t>
+          <t>4. Лист «Люди» необязательный: нужен, чтобы добавить человеку описание и ссылку.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
-          <t>5. Лист «Люди» необязательный: нужен, чтобы добавить человеку описание и ссылку.</t>
+          <t>Время вводите так: ч:мм:сс, например 0:20:52. Столбцы «Начало» и «Конец» в формате «простой текст»,</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
-        <is>
-          <t>Время вводите так: ч:мм:сс, например 0:20:52. Столбцы со временем в формате «простой текст»,</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
         <is>
           <t>не меняйте формат: иначе Google превратит 20:52 в 20 часов 52 минуты.</t>
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Не переименовывайте листы и не меняйте заголовки в первой строке.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>ID номера — короткий код из латинских букв, цифр, дефиса: он станет частью адреса страницы.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>После того как номер опубликован, ID лучше не менять: сменится адрес страницы.</t>
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+    </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Если в таблице ошибка, сайт не обновится, а в отчёте сборки будет написано, на каком листе и в какой строке.</t>
         </is>
@@ -5850,3547 +5821,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID номера</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Время</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Подпись</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Номер (подсказка, не трогать)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="n"/>
-      <c r="D2" s="5">
-        <f>IF(A2="","",IFERROR(VLOOKUP(A2,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="3" t="n"/>
-      <c r="D3" s="5">
-        <f>IF(A3="","",IFERROR(VLOOKUP(A3,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="3" t="n"/>
-      <c r="D4" s="5">
-        <f>IF(A4="","",IFERROR(VLOOKUP(A4,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="3" t="n"/>
-      <c r="D5" s="5">
-        <f>IF(A5="","",IFERROR(VLOOKUP(A5,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="3" t="n"/>
-      <c r="D6" s="5">
-        <f>IF(A6="","",IFERROR(VLOOKUP(A6,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="3" t="n"/>
-      <c r="D7" s="5">
-        <f>IF(A7="","",IFERROR(VLOOKUP(A7,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="3" t="n"/>
-      <c r="D8" s="5">
-        <f>IF(A8="","",IFERROR(VLOOKUP(A8,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="3" t="n"/>
-      <c r="D9" s="5">
-        <f>IF(A9="","",IFERROR(VLOOKUP(A9,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="3" t="n"/>
-      <c r="D10" s="5">
-        <f>IF(A10="","",IFERROR(VLOOKUP(A10,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="3" t="n"/>
-      <c r="D11" s="5">
-        <f>IF(A11="","",IFERROR(VLOOKUP(A11,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="3" t="n"/>
-      <c r="D12" s="5">
-        <f>IF(A12="","",IFERROR(VLOOKUP(A12,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="3" t="n"/>
-      <c r="D13" s="5">
-        <f>IF(A13="","",IFERROR(VLOOKUP(A13,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="3" t="n"/>
-      <c r="D14" s="5">
-        <f>IF(A14="","",IFERROR(VLOOKUP(A14,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="3" t="n"/>
-      <c r="D15" s="5">
-        <f>IF(A15="","",IFERROR(VLOOKUP(A15,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="3" t="n"/>
-      <c r="D16" s="5">
-        <f>IF(A16="","",IFERROR(VLOOKUP(A16,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="3" t="n"/>
-      <c r="D17" s="5">
-        <f>IF(A17="","",IFERROR(VLOOKUP(A17,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="3" t="n"/>
-      <c r="D18" s="5">
-        <f>IF(A18="","",IFERROR(VLOOKUP(A18,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="3" t="n"/>
-      <c r="D19" s="5">
-        <f>IF(A19="","",IFERROR(VLOOKUP(A19,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="3" t="n"/>
-      <c r="D20" s="5">
-        <f>IF(A20="","",IFERROR(VLOOKUP(A20,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="3" t="n"/>
-      <c r="D21" s="5">
-        <f>IF(A21="","",IFERROR(VLOOKUP(A21,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="3" t="n"/>
-      <c r="D22" s="5">
-        <f>IF(A22="","",IFERROR(VLOOKUP(A22,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="3" t="n"/>
-      <c r="D23" s="5">
-        <f>IF(A23="","",IFERROR(VLOOKUP(A23,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="3" t="n"/>
-      <c r="D24" s="5">
-        <f>IF(A24="","",IFERROR(VLOOKUP(A24,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="3" t="n"/>
-      <c r="D25" s="5">
-        <f>IF(A25="","",IFERROR(VLOOKUP(A25,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="3" t="n"/>
-      <c r="D26" s="5">
-        <f>IF(A26="","",IFERROR(VLOOKUP(A26,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="3" t="n"/>
-      <c r="D27" s="5">
-        <f>IF(A27="","",IFERROR(VLOOKUP(A27,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="3" t="n"/>
-      <c r="D28" s="5">
-        <f>IF(A28="","",IFERROR(VLOOKUP(A28,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="3" t="n"/>
-      <c r="D29" s="5">
-        <f>IF(A29="","",IFERROR(VLOOKUP(A29,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="3" t="n"/>
-      <c r="D30" s="5">
-        <f>IF(A30="","",IFERROR(VLOOKUP(A30,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="3" t="n"/>
-      <c r="D31" s="5">
-        <f>IF(A31="","",IFERROR(VLOOKUP(A31,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="3" t="n"/>
-      <c r="D32" s="5">
-        <f>IF(A32="","",IFERROR(VLOOKUP(A32,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="3" t="n"/>
-      <c r="D33" s="5">
-        <f>IF(A33="","",IFERROR(VLOOKUP(A33,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="3" t="n"/>
-      <c r="D34" s="5">
-        <f>IF(A34="","",IFERROR(VLOOKUP(A34,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="3" t="n"/>
-      <c r="D35" s="5">
-        <f>IF(A35="","",IFERROR(VLOOKUP(A35,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="3" t="n"/>
-      <c r="D36" s="5">
-        <f>IF(A36="","",IFERROR(VLOOKUP(A36,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="3" t="n"/>
-      <c r="D37" s="5">
-        <f>IF(A37="","",IFERROR(VLOOKUP(A37,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="3" t="n"/>
-      <c r="D38" s="5">
-        <f>IF(A38="","",IFERROR(VLOOKUP(A38,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="3" t="n"/>
-      <c r="D39" s="5">
-        <f>IF(A39="","",IFERROR(VLOOKUP(A39,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="3" t="n"/>
-      <c r="D40" s="5">
-        <f>IF(A40="","",IFERROR(VLOOKUP(A40,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="3" t="n"/>
-      <c r="D41" s="5">
-        <f>IF(A41="","",IFERROR(VLOOKUP(A41,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="3" t="n"/>
-      <c r="D42" s="5">
-        <f>IF(A42="","",IFERROR(VLOOKUP(A42,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="3" t="n"/>
-      <c r="D43" s="5">
-        <f>IF(A43="","",IFERROR(VLOOKUP(A43,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="3" t="n"/>
-      <c r="D44" s="5">
-        <f>IF(A44="","",IFERROR(VLOOKUP(A44,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="3" t="n"/>
-      <c r="D45" s="5">
-        <f>IF(A45="","",IFERROR(VLOOKUP(A45,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="3" t="n"/>
-      <c r="D46" s="5">
-        <f>IF(A46="","",IFERROR(VLOOKUP(A46,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="3" t="n"/>
-      <c r="D47" s="5">
-        <f>IF(A47="","",IFERROR(VLOOKUP(A47,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="3" t="n"/>
-      <c r="D48" s="5">
-        <f>IF(A48="","",IFERROR(VLOOKUP(A48,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="3" t="n"/>
-      <c r="D49" s="5">
-        <f>IF(A49="","",IFERROR(VLOOKUP(A49,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="3" t="n"/>
-      <c r="D50" s="5">
-        <f>IF(A50="","",IFERROR(VLOOKUP(A50,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="3" t="n"/>
-      <c r="D51" s="5">
-        <f>IF(A51="","",IFERROR(VLOOKUP(A51,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="3" t="n"/>
-      <c r="D52" s="5">
-        <f>IF(A52="","",IFERROR(VLOOKUP(A52,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="3" t="n"/>
-      <c r="D53" s="5">
-        <f>IF(A53="","",IFERROR(VLOOKUP(A53,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="3" t="n"/>
-      <c r="D54" s="5">
-        <f>IF(A54="","",IFERROR(VLOOKUP(A54,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="3" t="n"/>
-      <c r="D55" s="5">
-        <f>IF(A55="","",IFERROR(VLOOKUP(A55,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="3" t="n"/>
-      <c r="D56" s="5">
-        <f>IF(A56="","",IFERROR(VLOOKUP(A56,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="3" t="n"/>
-      <c r="D57" s="5">
-        <f>IF(A57="","",IFERROR(VLOOKUP(A57,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="3" t="n"/>
-      <c r="D58" s="5">
-        <f>IF(A58="","",IFERROR(VLOOKUP(A58,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="3" t="n"/>
-      <c r="D59" s="5">
-        <f>IF(A59="","",IFERROR(VLOOKUP(A59,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="3" t="n"/>
-      <c r="D60" s="5">
-        <f>IF(A60="","",IFERROR(VLOOKUP(A60,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="3" t="n"/>
-      <c r="D61" s="5">
-        <f>IF(A61="","",IFERROR(VLOOKUP(A61,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="3" t="n"/>
-      <c r="D62" s="5">
-        <f>IF(A62="","",IFERROR(VLOOKUP(A62,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="3" t="n"/>
-      <c r="D63" s="5">
-        <f>IF(A63="","",IFERROR(VLOOKUP(A63,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="3" t="n"/>
-      <c r="D64" s="5">
-        <f>IF(A64="","",IFERROR(VLOOKUP(A64,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="3" t="n"/>
-      <c r="D65" s="5">
-        <f>IF(A65="","",IFERROR(VLOOKUP(A65,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="3" t="n"/>
-      <c r="D66" s="5">
-        <f>IF(A66="","",IFERROR(VLOOKUP(A66,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="3" t="n"/>
-      <c r="D67" s="5">
-        <f>IF(A67="","",IFERROR(VLOOKUP(A67,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="3" t="n"/>
-      <c r="D68" s="5">
-        <f>IF(A68="","",IFERROR(VLOOKUP(A68,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="3" t="n"/>
-      <c r="D69" s="5">
-        <f>IF(A69="","",IFERROR(VLOOKUP(A69,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="3" t="n"/>
-      <c r="D70" s="5">
-        <f>IF(A70="","",IFERROR(VLOOKUP(A70,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="3" t="n"/>
-      <c r="D71" s="5">
-        <f>IF(A71="","",IFERROR(VLOOKUP(A71,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="3" t="n"/>
-      <c r="D72" s="5">
-        <f>IF(A72="","",IFERROR(VLOOKUP(A72,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="3" t="n"/>
-      <c r="D73" s="5">
-        <f>IF(A73="","",IFERROR(VLOOKUP(A73,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="3" t="n"/>
-      <c r="D74" s="5">
-        <f>IF(A74="","",IFERROR(VLOOKUP(A74,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="3" t="n"/>
-      <c r="D75" s="5">
-        <f>IF(A75="","",IFERROR(VLOOKUP(A75,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="3" t="n"/>
-      <c r="D76" s="5">
-        <f>IF(A76="","",IFERROR(VLOOKUP(A76,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="3" t="n"/>
-      <c r="D77" s="5">
-        <f>IF(A77="","",IFERROR(VLOOKUP(A77,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="3" t="n"/>
-      <c r="D78" s="5">
-        <f>IF(A78="","",IFERROR(VLOOKUP(A78,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="3" t="n"/>
-      <c r="D79" s="5">
-        <f>IF(A79="","",IFERROR(VLOOKUP(A79,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="3" t="n"/>
-      <c r="D80" s="5">
-        <f>IF(A80="","",IFERROR(VLOOKUP(A80,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="3" t="n"/>
-      <c r="D81" s="5">
-        <f>IF(A81="","",IFERROR(VLOOKUP(A81,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="3" t="n"/>
-      <c r="D82" s="5">
-        <f>IF(A82="","",IFERROR(VLOOKUP(A82,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="3" t="n"/>
-      <c r="D83" s="5">
-        <f>IF(A83="","",IFERROR(VLOOKUP(A83,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="3" t="n"/>
-      <c r="D84" s="5">
-        <f>IF(A84="","",IFERROR(VLOOKUP(A84,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="3" t="n"/>
-      <c r="D85" s="5">
-        <f>IF(A85="","",IFERROR(VLOOKUP(A85,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="3" t="n"/>
-      <c r="D86" s="5">
-        <f>IF(A86="","",IFERROR(VLOOKUP(A86,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="3" t="n"/>
-      <c r="D87" s="5">
-        <f>IF(A87="","",IFERROR(VLOOKUP(A87,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="3" t="n"/>
-      <c r="D88" s="5">
-        <f>IF(A88="","",IFERROR(VLOOKUP(A88,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="3" t="n"/>
-      <c r="D89" s="5">
-        <f>IF(A89="","",IFERROR(VLOOKUP(A89,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="3" t="n"/>
-      <c r="D90" s="5">
-        <f>IF(A90="","",IFERROR(VLOOKUP(A90,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="3" t="n"/>
-      <c r="D91" s="5">
-        <f>IF(A91="","",IFERROR(VLOOKUP(A91,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="3" t="n"/>
-      <c r="D92" s="5">
-        <f>IF(A92="","",IFERROR(VLOOKUP(A92,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="3" t="n"/>
-      <c r="D93" s="5">
-        <f>IF(A93="","",IFERROR(VLOOKUP(A93,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="3" t="n"/>
-      <c r="D94" s="5">
-        <f>IF(A94="","",IFERROR(VLOOKUP(A94,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="3" t="n"/>
-      <c r="D95" s="5">
-        <f>IF(A95="","",IFERROR(VLOOKUP(A95,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="3" t="n"/>
-      <c r="D96" s="5">
-        <f>IF(A96="","",IFERROR(VLOOKUP(A96,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="3" t="n"/>
-      <c r="D97" s="5">
-        <f>IF(A97="","",IFERROR(VLOOKUP(A97,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="3" t="n"/>
-      <c r="D98" s="5">
-        <f>IF(A98="","",IFERROR(VLOOKUP(A98,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="3" t="n"/>
-      <c r="D99" s="5">
-        <f>IF(A99="","",IFERROR(VLOOKUP(A99,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="3" t="n"/>
-      <c r="D100" s="5">
-        <f>IF(A100="","",IFERROR(VLOOKUP(A100,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="3" t="n"/>
-      <c r="D101" s="5">
-        <f>IF(A101="","",IFERROR(VLOOKUP(A101,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="3" t="n"/>
-      <c r="D102" s="5">
-        <f>IF(A102="","",IFERROR(VLOOKUP(A102,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="3" t="n"/>
-      <c r="D103" s="5">
-        <f>IF(A103="","",IFERROR(VLOOKUP(A103,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="3" t="n"/>
-      <c r="D104" s="5">
-        <f>IF(A104="","",IFERROR(VLOOKUP(A104,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="3" t="n"/>
-      <c r="D105" s="5">
-        <f>IF(A105="","",IFERROR(VLOOKUP(A105,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" s="3" t="n"/>
-      <c r="D106" s="5">
-        <f>IF(A106="","",IFERROR(VLOOKUP(A106,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="3" t="n"/>
-      <c r="D107" s="5">
-        <f>IF(A107="","",IFERROR(VLOOKUP(A107,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" s="3" t="n"/>
-      <c r="D108" s="5">
-        <f>IF(A108="","",IFERROR(VLOOKUP(A108,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109">
-      <c r="B109" s="3" t="n"/>
-      <c r="D109" s="5">
-        <f>IF(A109="","",IFERROR(VLOOKUP(A109,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" s="3" t="n"/>
-      <c r="D110" s="5">
-        <f>IF(A110="","",IFERROR(VLOOKUP(A110,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="B111" s="3" t="n"/>
-      <c r="D111" s="5">
-        <f>IF(A111="","",IFERROR(VLOOKUP(A111,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="3" t="n"/>
-      <c r="D112" s="5">
-        <f>IF(A112="","",IFERROR(VLOOKUP(A112,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="B113" s="3" t="n"/>
-      <c r="D113" s="5">
-        <f>IF(A113="","",IFERROR(VLOOKUP(A113,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="B114" s="3" t="n"/>
-      <c r="D114" s="5">
-        <f>IF(A114="","",IFERROR(VLOOKUP(A114,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="3" t="n"/>
-      <c r="D115" s="5">
-        <f>IF(A115="","",IFERROR(VLOOKUP(A115,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" s="3" t="n"/>
-      <c r="D116" s="5">
-        <f>IF(A116="","",IFERROR(VLOOKUP(A116,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" s="3" t="n"/>
-      <c r="D117" s="5">
-        <f>IF(A117="","",IFERROR(VLOOKUP(A117,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" s="3" t="n"/>
-      <c r="D118" s="5">
-        <f>IF(A118="","",IFERROR(VLOOKUP(A118,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" s="3" t="n"/>
-      <c r="D119" s="5">
-        <f>IF(A119="","",IFERROR(VLOOKUP(A119,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" s="3" t="n"/>
-      <c r="D120" s="5">
-        <f>IF(A120="","",IFERROR(VLOOKUP(A120,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="B121" s="3" t="n"/>
-      <c r="D121" s="5">
-        <f>IF(A121="","",IFERROR(VLOOKUP(A121,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122">
-      <c r="B122" s="3" t="n"/>
-      <c r="D122" s="5">
-        <f>IF(A122="","",IFERROR(VLOOKUP(A122,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" s="3" t="n"/>
-      <c r="D123" s="5">
-        <f>IF(A123="","",IFERROR(VLOOKUP(A123,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" s="3" t="n"/>
-      <c r="D124" s="5">
-        <f>IF(A124="","",IFERROR(VLOOKUP(A124,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" s="3" t="n"/>
-      <c r="D125" s="5">
-        <f>IF(A125="","",IFERROR(VLOOKUP(A125,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="3" t="n"/>
-      <c r="D126" s="5">
-        <f>IF(A126="","",IFERROR(VLOOKUP(A126,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="3" t="n"/>
-      <c r="D127" s="5">
-        <f>IF(A127="","",IFERROR(VLOOKUP(A127,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="3" t="n"/>
-      <c r="D128" s="5">
-        <f>IF(A128="","",IFERROR(VLOOKUP(A128,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="B129" s="3" t="n"/>
-      <c r="D129" s="5">
-        <f>IF(A129="","",IFERROR(VLOOKUP(A129,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" s="3" t="n"/>
-      <c r="D130" s="5">
-        <f>IF(A130="","",IFERROR(VLOOKUP(A130,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="B131" s="3" t="n"/>
-      <c r="D131" s="5">
-        <f>IF(A131="","",IFERROR(VLOOKUP(A131,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="B132" s="3" t="n"/>
-      <c r="D132" s="5">
-        <f>IF(A132="","",IFERROR(VLOOKUP(A132,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="B133" s="3" t="n"/>
-      <c r="D133" s="5">
-        <f>IF(A133="","",IFERROR(VLOOKUP(A133,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" s="3" t="n"/>
-      <c r="D134" s="5">
-        <f>IF(A134="","",IFERROR(VLOOKUP(A134,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" s="3" t="n"/>
-      <c r="D135" s="5">
-        <f>IF(A135="","",IFERROR(VLOOKUP(A135,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="B136" s="3" t="n"/>
-      <c r="D136" s="5">
-        <f>IF(A136="","",IFERROR(VLOOKUP(A136,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="B137" s="3" t="n"/>
-      <c r="D137" s="5">
-        <f>IF(A137="","",IFERROR(VLOOKUP(A137,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="B138" s="3" t="n"/>
-      <c r="D138" s="5">
-        <f>IF(A138="","",IFERROR(VLOOKUP(A138,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139">
-      <c r="B139" s="3" t="n"/>
-      <c r="D139" s="5">
-        <f>IF(A139="","",IFERROR(VLOOKUP(A139,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="B140" s="3" t="n"/>
-      <c r="D140" s="5">
-        <f>IF(A140="","",IFERROR(VLOOKUP(A140,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141">
-      <c r="B141" s="3" t="n"/>
-      <c r="D141" s="5">
-        <f>IF(A141="","",IFERROR(VLOOKUP(A141,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="B142" s="3" t="n"/>
-      <c r="D142" s="5">
-        <f>IF(A142="","",IFERROR(VLOOKUP(A142,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143">
-      <c r="B143" s="3" t="n"/>
-      <c r="D143" s="5">
-        <f>IF(A143="","",IFERROR(VLOOKUP(A143,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="B144" s="3" t="n"/>
-      <c r="D144" s="5">
-        <f>IF(A144="","",IFERROR(VLOOKUP(A144,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145">
-      <c r="B145" s="3" t="n"/>
-      <c r="D145" s="5">
-        <f>IF(A145="","",IFERROR(VLOOKUP(A145,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="B146" s="3" t="n"/>
-      <c r="D146" s="5">
-        <f>IF(A146="","",IFERROR(VLOOKUP(A146,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="B147" s="3" t="n"/>
-      <c r="D147" s="5">
-        <f>IF(A147="","",IFERROR(VLOOKUP(A147,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="B148" s="3" t="n"/>
-      <c r="D148" s="5">
-        <f>IF(A148="","",IFERROR(VLOOKUP(A148,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="B149" s="3" t="n"/>
-      <c r="D149" s="5">
-        <f>IF(A149="","",IFERROR(VLOOKUP(A149,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="B150" s="3" t="n"/>
-      <c r="D150" s="5">
-        <f>IF(A150="","",IFERROR(VLOOKUP(A150,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151">
-      <c r="B151" s="3" t="n"/>
-      <c r="D151" s="5">
-        <f>IF(A151="","",IFERROR(VLOOKUP(A151,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="B152" s="3" t="n"/>
-      <c r="D152" s="5">
-        <f>IF(A152="","",IFERROR(VLOOKUP(A152,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153">
-      <c r="B153" s="3" t="n"/>
-      <c r="D153" s="5">
-        <f>IF(A153="","",IFERROR(VLOOKUP(A153,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154">
-      <c r="B154" s="3" t="n"/>
-      <c r="D154" s="5">
-        <f>IF(A154="","",IFERROR(VLOOKUP(A154,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155">
-      <c r="B155" s="3" t="n"/>
-      <c r="D155" s="5">
-        <f>IF(A155="","",IFERROR(VLOOKUP(A155,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156">
-      <c r="B156" s="3" t="n"/>
-      <c r="D156" s="5">
-        <f>IF(A156="","",IFERROR(VLOOKUP(A156,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157">
-      <c r="B157" s="3" t="n"/>
-      <c r="D157" s="5">
-        <f>IF(A157="","",IFERROR(VLOOKUP(A157,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158">
-      <c r="B158" s="3" t="n"/>
-      <c r="D158" s="5">
-        <f>IF(A158="","",IFERROR(VLOOKUP(A158,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159">
-      <c r="B159" s="3" t="n"/>
-      <c r="D159" s="5">
-        <f>IF(A159="","",IFERROR(VLOOKUP(A159,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160">
-      <c r="B160" s="3" t="n"/>
-      <c r="D160" s="5">
-        <f>IF(A160="","",IFERROR(VLOOKUP(A160,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161">
-      <c r="B161" s="3" t="n"/>
-      <c r="D161" s="5">
-        <f>IF(A161="","",IFERROR(VLOOKUP(A161,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162">
-      <c r="B162" s="3" t="n"/>
-      <c r="D162" s="5">
-        <f>IF(A162="","",IFERROR(VLOOKUP(A162,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163">
-      <c r="B163" s="3" t="n"/>
-      <c r="D163" s="5">
-        <f>IF(A163="","",IFERROR(VLOOKUP(A163,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164">
-      <c r="B164" s="3" t="n"/>
-      <c r="D164" s="5">
-        <f>IF(A164="","",IFERROR(VLOOKUP(A164,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165">
-      <c r="B165" s="3" t="n"/>
-      <c r="D165" s="5">
-        <f>IF(A165="","",IFERROR(VLOOKUP(A165,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166">
-      <c r="B166" s="3" t="n"/>
-      <c r="D166" s="5">
-        <f>IF(A166="","",IFERROR(VLOOKUP(A166,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167">
-      <c r="B167" s="3" t="n"/>
-      <c r="D167" s="5">
-        <f>IF(A167="","",IFERROR(VLOOKUP(A167,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168">
-      <c r="B168" s="3" t="n"/>
-      <c r="D168" s="5">
-        <f>IF(A168="","",IFERROR(VLOOKUP(A168,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169">
-      <c r="B169" s="3" t="n"/>
-      <c r="D169" s="5">
-        <f>IF(A169="","",IFERROR(VLOOKUP(A169,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170">
-      <c r="B170" s="3" t="n"/>
-      <c r="D170" s="5">
-        <f>IF(A170="","",IFERROR(VLOOKUP(A170,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171">
-      <c r="B171" s="3" t="n"/>
-      <c r="D171" s="5">
-        <f>IF(A171="","",IFERROR(VLOOKUP(A171,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172">
-      <c r="B172" s="3" t="n"/>
-      <c r="D172" s="5">
-        <f>IF(A172="","",IFERROR(VLOOKUP(A172,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173">
-      <c r="B173" s="3" t="n"/>
-      <c r="D173" s="5">
-        <f>IF(A173="","",IFERROR(VLOOKUP(A173,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174">
-      <c r="B174" s="3" t="n"/>
-      <c r="D174" s="5">
-        <f>IF(A174="","",IFERROR(VLOOKUP(A174,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175">
-      <c r="B175" s="3" t="n"/>
-      <c r="D175" s="5">
-        <f>IF(A175="","",IFERROR(VLOOKUP(A175,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="B176" s="3" t="n"/>
-      <c r="D176" s="5">
-        <f>IF(A176="","",IFERROR(VLOOKUP(A176,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="B177" s="3" t="n"/>
-      <c r="D177" s="5">
-        <f>IF(A177="","",IFERROR(VLOOKUP(A177,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="B178" s="3" t="n"/>
-      <c r="D178" s="5">
-        <f>IF(A178="","",IFERROR(VLOOKUP(A178,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="B179" s="3" t="n"/>
-      <c r="D179" s="5">
-        <f>IF(A179="","",IFERROR(VLOOKUP(A179,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180">
-      <c r="B180" s="3" t="n"/>
-      <c r="D180" s="5">
-        <f>IF(A180="","",IFERROR(VLOOKUP(A180,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="B181" s="3" t="n"/>
-      <c r="D181" s="5">
-        <f>IF(A181="","",IFERROR(VLOOKUP(A181,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="B182" s="3" t="n"/>
-      <c r="D182" s="5">
-        <f>IF(A182="","",IFERROR(VLOOKUP(A182,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="B183" s="3" t="n"/>
-      <c r="D183" s="5">
-        <f>IF(A183="","",IFERROR(VLOOKUP(A183,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="B184" s="3" t="n"/>
-      <c r="D184" s="5">
-        <f>IF(A184="","",IFERROR(VLOOKUP(A184,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="B185" s="3" t="n"/>
-      <c r="D185" s="5">
-        <f>IF(A185="","",IFERROR(VLOOKUP(A185,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="B186" s="3" t="n"/>
-      <c r="D186" s="5">
-        <f>IF(A186="","",IFERROR(VLOOKUP(A186,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="B187" s="3" t="n"/>
-      <c r="D187" s="5">
-        <f>IF(A187="","",IFERROR(VLOOKUP(A187,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="188">
-      <c r="B188" s="3" t="n"/>
-      <c r="D188" s="5">
-        <f>IF(A188="","",IFERROR(VLOOKUP(A188,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="189">
-      <c r="B189" s="3" t="n"/>
-      <c r="D189" s="5">
-        <f>IF(A189="","",IFERROR(VLOOKUP(A189,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="190">
-      <c r="B190" s="3" t="n"/>
-      <c r="D190" s="5">
-        <f>IF(A190="","",IFERROR(VLOOKUP(A190,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="191">
-      <c r="B191" s="3" t="n"/>
-      <c r="D191" s="5">
-        <f>IF(A191="","",IFERROR(VLOOKUP(A191,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192">
-      <c r="B192" s="3" t="n"/>
-      <c r="D192" s="5">
-        <f>IF(A192="","",IFERROR(VLOOKUP(A192,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="193">
-      <c r="B193" s="3" t="n"/>
-      <c r="D193" s="5">
-        <f>IF(A193="","",IFERROR(VLOOKUP(A193,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194">
-      <c r="B194" s="3" t="n"/>
-      <c r="D194" s="5">
-        <f>IF(A194="","",IFERROR(VLOOKUP(A194,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195">
-      <c r="B195" s="3" t="n"/>
-      <c r="D195" s="5">
-        <f>IF(A195="","",IFERROR(VLOOKUP(A195,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196">
-      <c r="B196" s="3" t="n"/>
-      <c r="D196" s="5">
-        <f>IF(A196="","",IFERROR(VLOOKUP(A196,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197">
-      <c r="B197" s="3" t="n"/>
-      <c r="D197" s="5">
-        <f>IF(A197="","",IFERROR(VLOOKUP(A197,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198">
-      <c r="B198" s="3" t="n"/>
-      <c r="D198" s="5">
-        <f>IF(A198="","",IFERROR(VLOOKUP(A198,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199">
-      <c r="B199" s="3" t="n"/>
-      <c r="D199" s="5">
-        <f>IF(A199="","",IFERROR(VLOOKUP(A199,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="200">
-      <c r="B200" s="3" t="n"/>
-      <c r="D200" s="5">
-        <f>IF(A200="","",IFERROR(VLOOKUP(A200,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="201">
-      <c r="B201" s="3" t="n"/>
-      <c r="D201" s="5">
-        <f>IF(A201="","",IFERROR(VLOOKUP(A201,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="202">
-      <c r="B202" s="3" t="n"/>
-      <c r="D202" s="5">
-        <f>IF(A202="","",IFERROR(VLOOKUP(A202,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="203">
-      <c r="B203" s="3" t="n"/>
-      <c r="D203" s="5">
-        <f>IF(A203="","",IFERROR(VLOOKUP(A203,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="204">
-      <c r="B204" s="3" t="n"/>
-      <c r="D204" s="5">
-        <f>IF(A204="","",IFERROR(VLOOKUP(A204,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="205">
-      <c r="B205" s="3" t="n"/>
-      <c r="D205" s="5">
-        <f>IF(A205="","",IFERROR(VLOOKUP(A205,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="206">
-      <c r="B206" s="3" t="n"/>
-      <c r="D206" s="5">
-        <f>IF(A206="","",IFERROR(VLOOKUP(A206,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="207">
-      <c r="B207" s="3" t="n"/>
-      <c r="D207" s="5">
-        <f>IF(A207="","",IFERROR(VLOOKUP(A207,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208">
-      <c r="B208" s="3" t="n"/>
-      <c r="D208" s="5">
-        <f>IF(A208="","",IFERROR(VLOOKUP(A208,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="209">
-      <c r="B209" s="3" t="n"/>
-      <c r="D209" s="5">
-        <f>IF(A209="","",IFERROR(VLOOKUP(A209,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210">
-      <c r="B210" s="3" t="n"/>
-      <c r="D210" s="5">
-        <f>IF(A210="","",IFERROR(VLOOKUP(A210,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="211">
-      <c r="B211" s="3" t="n"/>
-      <c r="D211" s="5">
-        <f>IF(A211="","",IFERROR(VLOOKUP(A211,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="212">
-      <c r="B212" s="3" t="n"/>
-      <c r="D212" s="5">
-        <f>IF(A212="","",IFERROR(VLOOKUP(A212,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="213">
-      <c r="B213" s="3" t="n"/>
-      <c r="D213" s="5">
-        <f>IF(A213="","",IFERROR(VLOOKUP(A213,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="214">
-      <c r="B214" s="3" t="n"/>
-      <c r="D214" s="5">
-        <f>IF(A214="","",IFERROR(VLOOKUP(A214,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="215">
-      <c r="B215" s="3" t="n"/>
-      <c r="D215" s="5">
-        <f>IF(A215="","",IFERROR(VLOOKUP(A215,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="216">
-      <c r="B216" s="3" t="n"/>
-      <c r="D216" s="5">
-        <f>IF(A216="","",IFERROR(VLOOKUP(A216,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="217">
-      <c r="B217" s="3" t="n"/>
-      <c r="D217" s="5">
-        <f>IF(A217="","",IFERROR(VLOOKUP(A217,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="218">
-      <c r="B218" s="3" t="n"/>
-      <c r="D218" s="5">
-        <f>IF(A218="","",IFERROR(VLOOKUP(A218,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="219">
-      <c r="B219" s="3" t="n"/>
-      <c r="D219" s="5">
-        <f>IF(A219="","",IFERROR(VLOOKUP(A219,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="220">
-      <c r="B220" s="3" t="n"/>
-      <c r="D220" s="5">
-        <f>IF(A220="","",IFERROR(VLOOKUP(A220,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="221">
-      <c r="B221" s="3" t="n"/>
-      <c r="D221" s="5">
-        <f>IF(A221="","",IFERROR(VLOOKUP(A221,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="222">
-      <c r="B222" s="3" t="n"/>
-      <c r="D222" s="5">
-        <f>IF(A222="","",IFERROR(VLOOKUP(A222,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="223">
-      <c r="B223" s="3" t="n"/>
-      <c r="D223" s="5">
-        <f>IF(A223="","",IFERROR(VLOOKUP(A223,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="224">
-      <c r="B224" s="3" t="n"/>
-      <c r="D224" s="5">
-        <f>IF(A224="","",IFERROR(VLOOKUP(A224,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="225">
-      <c r="B225" s="3" t="n"/>
-      <c r="D225" s="5">
-        <f>IF(A225="","",IFERROR(VLOOKUP(A225,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="226">
-      <c r="B226" s="3" t="n"/>
-      <c r="D226" s="5">
-        <f>IF(A226="","",IFERROR(VLOOKUP(A226,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227">
-      <c r="B227" s="3" t="n"/>
-      <c r="D227" s="5">
-        <f>IF(A227="","",IFERROR(VLOOKUP(A227,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228">
-      <c r="B228" s="3" t="n"/>
-      <c r="D228" s="5">
-        <f>IF(A228="","",IFERROR(VLOOKUP(A228,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229">
-      <c r="B229" s="3" t="n"/>
-      <c r="D229" s="5">
-        <f>IF(A229="","",IFERROR(VLOOKUP(A229,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230">
-      <c r="B230" s="3" t="n"/>
-      <c r="D230" s="5">
-        <f>IF(A230="","",IFERROR(VLOOKUP(A230,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231">
-      <c r="B231" s="3" t="n"/>
-      <c r="D231" s="5">
-        <f>IF(A231="","",IFERROR(VLOOKUP(A231,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232">
-      <c r="B232" s="3" t="n"/>
-      <c r="D232" s="5">
-        <f>IF(A232="","",IFERROR(VLOOKUP(A232,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="233">
-      <c r="B233" s="3" t="n"/>
-      <c r="D233" s="5">
-        <f>IF(A233="","",IFERROR(VLOOKUP(A233,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="234">
-      <c r="B234" s="3" t="n"/>
-      <c r="D234" s="5">
-        <f>IF(A234="","",IFERROR(VLOOKUP(A234,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="235">
-      <c r="B235" s="3" t="n"/>
-      <c r="D235" s="5">
-        <f>IF(A235="","",IFERROR(VLOOKUP(A235,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="236">
-      <c r="B236" s="3" t="n"/>
-      <c r="D236" s="5">
-        <f>IF(A236="","",IFERROR(VLOOKUP(A236,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="237">
-      <c r="B237" s="3" t="n"/>
-      <c r="D237" s="5">
-        <f>IF(A237="","",IFERROR(VLOOKUP(A237,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238">
-      <c r="B238" s="3" t="n"/>
-      <c r="D238" s="5">
-        <f>IF(A238="","",IFERROR(VLOOKUP(A238,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239">
-      <c r="B239" s="3" t="n"/>
-      <c r="D239" s="5">
-        <f>IF(A239="","",IFERROR(VLOOKUP(A239,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240">
-      <c r="B240" s="3" t="n"/>
-      <c r="D240" s="5">
-        <f>IF(A240="","",IFERROR(VLOOKUP(A240,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241">
-      <c r="B241" s="3" t="n"/>
-      <c r="D241" s="5">
-        <f>IF(A241="","",IFERROR(VLOOKUP(A241,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242">
-      <c r="B242" s="3" t="n"/>
-      <c r="D242" s="5">
-        <f>IF(A242="","",IFERROR(VLOOKUP(A242,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243">
-      <c r="B243" s="3" t="n"/>
-      <c r="D243" s="5">
-        <f>IF(A243="","",IFERROR(VLOOKUP(A243,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244">
-      <c r="B244" s="3" t="n"/>
-      <c r="D244" s="5">
-        <f>IF(A244="","",IFERROR(VLOOKUP(A244,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245">
-      <c r="B245" s="3" t="n"/>
-      <c r="D245" s="5">
-        <f>IF(A245="","",IFERROR(VLOOKUP(A245,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="246">
-      <c r="B246" s="3" t="n"/>
-      <c r="D246" s="5">
-        <f>IF(A246="","",IFERROR(VLOOKUP(A246,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247">
-      <c r="B247" s="3" t="n"/>
-      <c r="D247" s="5">
-        <f>IF(A247="","",IFERROR(VLOOKUP(A247,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248">
-      <c r="B248" s="3" t="n"/>
-      <c r="D248" s="5">
-        <f>IF(A248="","",IFERROR(VLOOKUP(A248,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249">
-      <c r="B249" s="3" t="n"/>
-      <c r="D249" s="5">
-        <f>IF(A249="","",IFERROR(VLOOKUP(A249,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="250">
-      <c r="B250" s="3" t="n"/>
-      <c r="D250" s="5">
-        <f>IF(A250="","",IFERROR(VLOOKUP(A250,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="251">
-      <c r="B251" s="3" t="n"/>
-      <c r="D251" s="5">
-        <f>IF(A251="","",IFERROR(VLOOKUP(A251,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252">
-      <c r="B252" s="3" t="n"/>
-      <c r="D252" s="5">
-        <f>IF(A252="","",IFERROR(VLOOKUP(A252,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253">
-      <c r="B253" s="3" t="n"/>
-      <c r="D253" s="5">
-        <f>IF(A253="","",IFERROR(VLOOKUP(A253,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254">
-      <c r="B254" s="3" t="n"/>
-      <c r="D254" s="5">
-        <f>IF(A254="","",IFERROR(VLOOKUP(A254,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255">
-      <c r="B255" s="3" t="n"/>
-      <c r="D255" s="5">
-        <f>IF(A255="","",IFERROR(VLOOKUP(A255,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256">
-      <c r="B256" s="3" t="n"/>
-      <c r="D256" s="5">
-        <f>IF(A256="","",IFERROR(VLOOKUP(A256,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="257">
-      <c r="B257" s="3" t="n"/>
-      <c r="D257" s="5">
-        <f>IF(A257="","",IFERROR(VLOOKUP(A257,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="258">
-      <c r="B258" s="3" t="n"/>
-      <c r="D258" s="5">
-        <f>IF(A258="","",IFERROR(VLOOKUP(A258,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="259">
-      <c r="B259" s="3" t="n"/>
-      <c r="D259" s="5">
-        <f>IF(A259="","",IFERROR(VLOOKUP(A259,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260">
-      <c r="B260" s="3" t="n"/>
-      <c r="D260" s="5">
-        <f>IF(A260="","",IFERROR(VLOOKUP(A260,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="261">
-      <c r="B261" s="3" t="n"/>
-      <c r="D261" s="5">
-        <f>IF(A261="","",IFERROR(VLOOKUP(A261,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="262">
-      <c r="B262" s="3" t="n"/>
-      <c r="D262" s="5">
-        <f>IF(A262="","",IFERROR(VLOOKUP(A262,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="263">
-      <c r="B263" s="3" t="n"/>
-      <c r="D263" s="5">
-        <f>IF(A263="","",IFERROR(VLOOKUP(A263,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="264">
-      <c r="B264" s="3" t="n"/>
-      <c r="D264" s="5">
-        <f>IF(A264="","",IFERROR(VLOOKUP(A264,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="265">
-      <c r="B265" s="3" t="n"/>
-      <c r="D265" s="5">
-        <f>IF(A265="","",IFERROR(VLOOKUP(A265,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="266">
-      <c r="B266" s="3" t="n"/>
-      <c r="D266" s="5">
-        <f>IF(A266="","",IFERROR(VLOOKUP(A266,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="267">
-      <c r="B267" s="3" t="n"/>
-      <c r="D267" s="5">
-        <f>IF(A267="","",IFERROR(VLOOKUP(A267,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268">
-      <c r="B268" s="3" t="n"/>
-      <c r="D268" s="5">
-        <f>IF(A268="","",IFERROR(VLOOKUP(A268,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269">
-      <c r="B269" s="3" t="n"/>
-      <c r="D269" s="5">
-        <f>IF(A269="","",IFERROR(VLOOKUP(A269,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="270">
-      <c r="B270" s="3" t="n"/>
-      <c r="D270" s="5">
-        <f>IF(A270="","",IFERROR(VLOOKUP(A270,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="271">
-      <c r="B271" s="3" t="n"/>
-      <c r="D271" s="5">
-        <f>IF(A271="","",IFERROR(VLOOKUP(A271,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="272">
-      <c r="B272" s="3" t="n"/>
-      <c r="D272" s="5">
-        <f>IF(A272="","",IFERROR(VLOOKUP(A272,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="273">
-      <c r="B273" s="3" t="n"/>
-      <c r="D273" s="5">
-        <f>IF(A273="","",IFERROR(VLOOKUP(A273,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="274">
-      <c r="B274" s="3" t="n"/>
-      <c r="D274" s="5">
-        <f>IF(A274="","",IFERROR(VLOOKUP(A274,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="275">
-      <c r="B275" s="3" t="n"/>
-      <c r="D275" s="5">
-        <f>IF(A275="","",IFERROR(VLOOKUP(A275,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="276">
-      <c r="B276" s="3" t="n"/>
-      <c r="D276" s="5">
-        <f>IF(A276="","",IFERROR(VLOOKUP(A276,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="277">
-      <c r="B277" s="3" t="n"/>
-      <c r="D277" s="5">
-        <f>IF(A277="","",IFERROR(VLOOKUP(A277,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="278">
-      <c r="B278" s="3" t="n"/>
-      <c r="D278" s="5">
-        <f>IF(A278="","",IFERROR(VLOOKUP(A278,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="279">
-      <c r="B279" s="3" t="n"/>
-      <c r="D279" s="5">
-        <f>IF(A279="","",IFERROR(VLOOKUP(A279,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="280">
-      <c r="B280" s="3" t="n"/>
-      <c r="D280" s="5">
-        <f>IF(A280="","",IFERROR(VLOOKUP(A280,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="281">
-      <c r="B281" s="3" t="n"/>
-      <c r="D281" s="5">
-        <f>IF(A281="","",IFERROR(VLOOKUP(A281,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="282">
-      <c r="B282" s="3" t="n"/>
-      <c r="D282" s="5">
-        <f>IF(A282="","",IFERROR(VLOOKUP(A282,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="283">
-      <c r="B283" s="3" t="n"/>
-      <c r="D283" s="5">
-        <f>IF(A283="","",IFERROR(VLOOKUP(A283,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="284">
-      <c r="B284" s="3" t="n"/>
-      <c r="D284" s="5">
-        <f>IF(A284="","",IFERROR(VLOOKUP(A284,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="285">
-      <c r="B285" s="3" t="n"/>
-      <c r="D285" s="5">
-        <f>IF(A285="","",IFERROR(VLOOKUP(A285,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="286">
-      <c r="B286" s="3" t="n"/>
-      <c r="D286" s="5">
-        <f>IF(A286="","",IFERROR(VLOOKUP(A286,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="287">
-      <c r="B287" s="3" t="n"/>
-      <c r="D287" s="5">
-        <f>IF(A287="","",IFERROR(VLOOKUP(A287,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="288">
-      <c r="B288" s="3" t="n"/>
-      <c r="D288" s="5">
-        <f>IF(A288="","",IFERROR(VLOOKUP(A288,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="289">
-      <c r="B289" s="3" t="n"/>
-      <c r="D289" s="5">
-        <f>IF(A289="","",IFERROR(VLOOKUP(A289,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="290">
-      <c r="B290" s="3" t="n"/>
-      <c r="D290" s="5">
-        <f>IF(A290="","",IFERROR(VLOOKUP(A290,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="291">
-      <c r="B291" s="3" t="n"/>
-      <c r="D291" s="5">
-        <f>IF(A291="","",IFERROR(VLOOKUP(A291,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="292">
-      <c r="B292" s="3" t="n"/>
-      <c r="D292" s="5">
-        <f>IF(A292="","",IFERROR(VLOOKUP(A292,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="293">
-      <c r="B293" s="3" t="n"/>
-      <c r="D293" s="5">
-        <f>IF(A293="","",IFERROR(VLOOKUP(A293,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="294">
-      <c r="B294" s="3" t="n"/>
-      <c r="D294" s="5">
-        <f>IF(A294="","",IFERROR(VLOOKUP(A294,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="295">
-      <c r="B295" s="3" t="n"/>
-      <c r="D295" s="5">
-        <f>IF(A295="","",IFERROR(VLOOKUP(A295,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="296">
-      <c r="B296" s="3" t="n"/>
-      <c r="D296" s="5">
-        <f>IF(A296="","",IFERROR(VLOOKUP(A296,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="297">
-      <c r="B297" s="3" t="n"/>
-      <c r="D297" s="5">
-        <f>IF(A297="","",IFERROR(VLOOKUP(A297,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="298">
-      <c r="B298" s="3" t="n"/>
-      <c r="D298" s="5">
-        <f>IF(A298="","",IFERROR(VLOOKUP(A298,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="299">
-      <c r="B299" s="3" t="n"/>
-      <c r="D299" s="5">
-        <f>IF(A299="","",IFERROR(VLOOKUP(A299,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="300">
-      <c r="B300" s="3" t="n"/>
-      <c r="D300" s="5">
-        <f>IF(A300="","",IFERROR(VLOOKUP(A300,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="301">
-      <c r="B301" s="3" t="n"/>
-      <c r="D301" s="5">
-        <f>IF(A301="","",IFERROR(VLOOKUP(A301,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="302">
-      <c r="B302" s="3" t="n"/>
-      <c r="D302" s="5">
-        <f>IF(A302="","",IFERROR(VLOOKUP(A302,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="303">
-      <c r="B303" s="3" t="n"/>
-      <c r="D303" s="5">
-        <f>IF(A303="","",IFERROR(VLOOKUP(A303,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="304">
-      <c r="B304" s="3" t="n"/>
-      <c r="D304" s="5">
-        <f>IF(A304="","",IFERROR(VLOOKUP(A304,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="305">
-      <c r="B305" s="3" t="n"/>
-      <c r="D305" s="5">
-        <f>IF(A305="","",IFERROR(VLOOKUP(A305,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="306">
-      <c r="B306" s="3" t="n"/>
-      <c r="D306" s="5">
-        <f>IF(A306="","",IFERROR(VLOOKUP(A306,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="307">
-      <c r="B307" s="3" t="n"/>
-      <c r="D307" s="5">
-        <f>IF(A307="","",IFERROR(VLOOKUP(A307,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="308">
-      <c r="B308" s="3" t="n"/>
-      <c r="D308" s="5">
-        <f>IF(A308="","",IFERROR(VLOOKUP(A308,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="309">
-      <c r="B309" s="3" t="n"/>
-      <c r="D309" s="5">
-        <f>IF(A309="","",IFERROR(VLOOKUP(A309,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="310">
-      <c r="B310" s="3" t="n"/>
-      <c r="D310" s="5">
-        <f>IF(A310="","",IFERROR(VLOOKUP(A310,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="311">
-      <c r="B311" s="3" t="n"/>
-      <c r="D311" s="5">
-        <f>IF(A311="","",IFERROR(VLOOKUP(A311,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="312">
-      <c r="B312" s="3" t="n"/>
-      <c r="D312" s="5">
-        <f>IF(A312="","",IFERROR(VLOOKUP(A312,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="313">
-      <c r="B313" s="3" t="n"/>
-      <c r="D313" s="5">
-        <f>IF(A313="","",IFERROR(VLOOKUP(A313,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="314">
-      <c r="B314" s="3" t="n"/>
-      <c r="D314" s="5">
-        <f>IF(A314="","",IFERROR(VLOOKUP(A314,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="315">
-      <c r="B315" s="3" t="n"/>
-      <c r="D315" s="5">
-        <f>IF(A315="","",IFERROR(VLOOKUP(A315,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="316">
-      <c r="B316" s="3" t="n"/>
-      <c r="D316" s="5">
-        <f>IF(A316="","",IFERROR(VLOOKUP(A316,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="317">
-      <c r="B317" s="3" t="n"/>
-      <c r="D317" s="5">
-        <f>IF(A317="","",IFERROR(VLOOKUP(A317,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="318">
-      <c r="B318" s="3" t="n"/>
-      <c r="D318" s="5">
-        <f>IF(A318="","",IFERROR(VLOOKUP(A318,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="319">
-      <c r="B319" s="3" t="n"/>
-      <c r="D319" s="5">
-        <f>IF(A319="","",IFERROR(VLOOKUP(A319,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="320">
-      <c r="B320" s="3" t="n"/>
-      <c r="D320" s="5">
-        <f>IF(A320="","",IFERROR(VLOOKUP(A320,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="321">
-      <c r="B321" s="3" t="n"/>
-      <c r="D321" s="5">
-        <f>IF(A321="","",IFERROR(VLOOKUP(A321,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="322">
-      <c r="B322" s="3" t="n"/>
-      <c r="D322" s="5">
-        <f>IF(A322="","",IFERROR(VLOOKUP(A322,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="323">
-      <c r="B323" s="3" t="n"/>
-      <c r="D323" s="5">
-        <f>IF(A323="","",IFERROR(VLOOKUP(A323,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="324">
-      <c r="B324" s="3" t="n"/>
-      <c r="D324" s="5">
-        <f>IF(A324="","",IFERROR(VLOOKUP(A324,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="325">
-      <c r="B325" s="3" t="n"/>
-      <c r="D325" s="5">
-        <f>IF(A325="","",IFERROR(VLOOKUP(A325,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="326">
-      <c r="B326" s="3" t="n"/>
-      <c r="D326" s="5">
-        <f>IF(A326="","",IFERROR(VLOOKUP(A326,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="327">
-      <c r="B327" s="3" t="n"/>
-      <c r="D327" s="5">
-        <f>IF(A327="","",IFERROR(VLOOKUP(A327,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="328">
-      <c r="B328" s="3" t="n"/>
-      <c r="D328" s="5">
-        <f>IF(A328="","",IFERROR(VLOOKUP(A328,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="329">
-      <c r="B329" s="3" t="n"/>
-      <c r="D329" s="5">
-        <f>IF(A329="","",IFERROR(VLOOKUP(A329,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="330">
-      <c r="B330" s="3" t="n"/>
-      <c r="D330" s="5">
-        <f>IF(A330="","",IFERROR(VLOOKUP(A330,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="331">
-      <c r="B331" s="3" t="n"/>
-      <c r="D331" s="5">
-        <f>IF(A331="","",IFERROR(VLOOKUP(A331,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="332">
-      <c r="B332" s="3" t="n"/>
-      <c r="D332" s="5">
-        <f>IF(A332="","",IFERROR(VLOOKUP(A332,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="333">
-      <c r="B333" s="3" t="n"/>
-      <c r="D333" s="5">
-        <f>IF(A333="","",IFERROR(VLOOKUP(A333,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="334">
-      <c r="B334" s="3" t="n"/>
-      <c r="D334" s="5">
-        <f>IF(A334="","",IFERROR(VLOOKUP(A334,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="335">
-      <c r="B335" s="3" t="n"/>
-      <c r="D335" s="5">
-        <f>IF(A335="","",IFERROR(VLOOKUP(A335,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="336">
-      <c r="B336" s="3" t="n"/>
-      <c r="D336" s="5">
-        <f>IF(A336="","",IFERROR(VLOOKUP(A336,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="337">
-      <c r="B337" s="3" t="n"/>
-      <c r="D337" s="5">
-        <f>IF(A337="","",IFERROR(VLOOKUP(A337,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="338">
-      <c r="B338" s="3" t="n"/>
-      <c r="D338" s="5">
-        <f>IF(A338="","",IFERROR(VLOOKUP(A338,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="339">
-      <c r="B339" s="3" t="n"/>
-      <c r="D339" s="5">
-        <f>IF(A339="","",IFERROR(VLOOKUP(A339,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="340">
-      <c r="B340" s="3" t="n"/>
-      <c r="D340" s="5">
-        <f>IF(A340="","",IFERROR(VLOOKUP(A340,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="341">
-      <c r="B341" s="3" t="n"/>
-      <c r="D341" s="5">
-        <f>IF(A341="","",IFERROR(VLOOKUP(A341,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="342">
-      <c r="B342" s="3" t="n"/>
-      <c r="D342" s="5">
-        <f>IF(A342="","",IFERROR(VLOOKUP(A342,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="343">
-      <c r="B343" s="3" t="n"/>
-      <c r="D343" s="5">
-        <f>IF(A343="","",IFERROR(VLOOKUP(A343,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="344">
-      <c r="B344" s="3" t="n"/>
-      <c r="D344" s="5">
-        <f>IF(A344="","",IFERROR(VLOOKUP(A344,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="345">
-      <c r="B345" s="3" t="n"/>
-      <c r="D345" s="5">
-        <f>IF(A345="","",IFERROR(VLOOKUP(A345,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="346">
-      <c r="B346" s="3" t="n"/>
-      <c r="D346" s="5">
-        <f>IF(A346="","",IFERROR(VLOOKUP(A346,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="347">
-      <c r="B347" s="3" t="n"/>
-      <c r="D347" s="5">
-        <f>IF(A347="","",IFERROR(VLOOKUP(A347,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="348">
-      <c r="B348" s="3" t="n"/>
-      <c r="D348" s="5">
-        <f>IF(A348="","",IFERROR(VLOOKUP(A348,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="349">
-      <c r="B349" s="3" t="n"/>
-      <c r="D349" s="5">
-        <f>IF(A349="","",IFERROR(VLOOKUP(A349,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="350">
-      <c r="B350" s="3" t="n"/>
-      <c r="D350" s="5">
-        <f>IF(A350="","",IFERROR(VLOOKUP(A350,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="351">
-      <c r="B351" s="3" t="n"/>
-      <c r="D351" s="5">
-        <f>IF(A351="","",IFERROR(VLOOKUP(A351,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="352">
-      <c r="B352" s="3" t="n"/>
-      <c r="D352" s="5">
-        <f>IF(A352="","",IFERROR(VLOOKUP(A352,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="353">
-      <c r="B353" s="3" t="n"/>
-      <c r="D353" s="5">
-        <f>IF(A353="","",IFERROR(VLOOKUP(A353,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="354">
-      <c r="B354" s="3" t="n"/>
-      <c r="D354" s="5">
-        <f>IF(A354="","",IFERROR(VLOOKUP(A354,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="355">
-      <c r="B355" s="3" t="n"/>
-      <c r="D355" s="5">
-        <f>IF(A355="","",IFERROR(VLOOKUP(A355,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="356">
-      <c r="B356" s="3" t="n"/>
-      <c r="D356" s="5">
-        <f>IF(A356="","",IFERROR(VLOOKUP(A356,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="357">
-      <c r="B357" s="3" t="n"/>
-      <c r="D357" s="5">
-        <f>IF(A357="","",IFERROR(VLOOKUP(A357,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="358">
-      <c r="B358" s="3" t="n"/>
-      <c r="D358" s="5">
-        <f>IF(A358="","",IFERROR(VLOOKUP(A358,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="359">
-      <c r="B359" s="3" t="n"/>
-      <c r="D359" s="5">
-        <f>IF(A359="","",IFERROR(VLOOKUP(A359,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="360">
-      <c r="B360" s="3" t="n"/>
-      <c r="D360" s="5">
-        <f>IF(A360="","",IFERROR(VLOOKUP(A360,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="361">
-      <c r="B361" s="3" t="n"/>
-      <c r="D361" s="5">
-        <f>IF(A361="","",IFERROR(VLOOKUP(A361,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="362">
-      <c r="B362" s="3" t="n"/>
-      <c r="D362" s="5">
-        <f>IF(A362="","",IFERROR(VLOOKUP(A362,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="363">
-      <c r="B363" s="3" t="n"/>
-      <c r="D363" s="5">
-        <f>IF(A363="","",IFERROR(VLOOKUP(A363,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="364">
-      <c r="B364" s="3" t="n"/>
-      <c r="D364" s="5">
-        <f>IF(A364="","",IFERROR(VLOOKUP(A364,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="365">
-      <c r="B365" s="3" t="n"/>
-      <c r="D365" s="5">
-        <f>IF(A365="","",IFERROR(VLOOKUP(A365,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="366">
-      <c r="B366" s="3" t="n"/>
-      <c r="D366" s="5">
-        <f>IF(A366="","",IFERROR(VLOOKUP(A366,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="367">
-      <c r="B367" s="3" t="n"/>
-      <c r="D367" s="5">
-        <f>IF(A367="","",IFERROR(VLOOKUP(A367,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="368">
-      <c r="B368" s="3" t="n"/>
-      <c r="D368" s="5">
-        <f>IF(A368="","",IFERROR(VLOOKUP(A368,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="369">
-      <c r="B369" s="3" t="n"/>
-      <c r="D369" s="5">
-        <f>IF(A369="","",IFERROR(VLOOKUP(A369,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="370">
-      <c r="B370" s="3" t="n"/>
-      <c r="D370" s="5">
-        <f>IF(A370="","",IFERROR(VLOOKUP(A370,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="371">
-      <c r="B371" s="3" t="n"/>
-      <c r="D371" s="5">
-        <f>IF(A371="","",IFERROR(VLOOKUP(A371,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="372">
-      <c r="B372" s="3" t="n"/>
-      <c r="D372" s="5">
-        <f>IF(A372="","",IFERROR(VLOOKUP(A372,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="373">
-      <c r="B373" s="3" t="n"/>
-      <c r="D373" s="5">
-        <f>IF(A373="","",IFERROR(VLOOKUP(A373,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="374">
-      <c r="B374" s="3" t="n"/>
-      <c r="D374" s="5">
-        <f>IF(A374="","",IFERROR(VLOOKUP(A374,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="375">
-      <c r="B375" s="3" t="n"/>
-      <c r="D375" s="5">
-        <f>IF(A375="","",IFERROR(VLOOKUP(A375,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="376">
-      <c r="B376" s="3" t="n"/>
-      <c r="D376" s="5">
-        <f>IF(A376="","",IFERROR(VLOOKUP(A376,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="377">
-      <c r="B377" s="3" t="n"/>
-      <c r="D377" s="5">
-        <f>IF(A377="","",IFERROR(VLOOKUP(A377,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="378">
-      <c r="B378" s="3" t="n"/>
-      <c r="D378" s="5">
-        <f>IF(A378="","",IFERROR(VLOOKUP(A378,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="379">
-      <c r="B379" s="3" t="n"/>
-      <c r="D379" s="5">
-        <f>IF(A379="","",IFERROR(VLOOKUP(A379,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="380">
-      <c r="B380" s="3" t="n"/>
-      <c r="D380" s="5">
-        <f>IF(A380="","",IFERROR(VLOOKUP(A380,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="381">
-      <c r="B381" s="3" t="n"/>
-      <c r="D381" s="5">
-        <f>IF(A381="","",IFERROR(VLOOKUP(A381,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="382">
-      <c r="B382" s="3" t="n"/>
-      <c r="D382" s="5">
-        <f>IF(A382="","",IFERROR(VLOOKUP(A382,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="383">
-      <c r="B383" s="3" t="n"/>
-      <c r="D383" s="5">
-        <f>IF(A383="","",IFERROR(VLOOKUP(A383,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="384">
-      <c r="B384" s="3" t="n"/>
-      <c r="D384" s="5">
-        <f>IF(A384="","",IFERROR(VLOOKUP(A384,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="385">
-      <c r="B385" s="3" t="n"/>
-      <c r="D385" s="5">
-        <f>IF(A385="","",IFERROR(VLOOKUP(A385,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="386">
-      <c r="B386" s="3" t="n"/>
-      <c r="D386" s="5">
-        <f>IF(A386="","",IFERROR(VLOOKUP(A386,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="387">
-      <c r="B387" s="3" t="n"/>
-      <c r="D387" s="5">
-        <f>IF(A387="","",IFERROR(VLOOKUP(A387,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="388">
-      <c r="B388" s="3" t="n"/>
-      <c r="D388" s="5">
-        <f>IF(A388="","",IFERROR(VLOOKUP(A388,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="389">
-      <c r="B389" s="3" t="n"/>
-      <c r="D389" s="5">
-        <f>IF(A389="","",IFERROR(VLOOKUP(A389,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="390">
-      <c r="B390" s="3" t="n"/>
-      <c r="D390" s="5">
-        <f>IF(A390="","",IFERROR(VLOOKUP(A390,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="391">
-      <c r="B391" s="3" t="n"/>
-      <c r="D391" s="5">
-        <f>IF(A391="","",IFERROR(VLOOKUP(A391,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="392">
-      <c r="B392" s="3" t="n"/>
-      <c r="D392" s="5">
-        <f>IF(A392="","",IFERROR(VLOOKUP(A392,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="393">
-      <c r="B393" s="3" t="n"/>
-      <c r="D393" s="5">
-        <f>IF(A393="","",IFERROR(VLOOKUP(A393,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="394">
-      <c r="B394" s="3" t="n"/>
-      <c r="D394" s="5">
-        <f>IF(A394="","",IFERROR(VLOOKUP(A394,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="395">
-      <c r="B395" s="3" t="n"/>
-      <c r="D395" s="5">
-        <f>IF(A395="","",IFERROR(VLOOKUP(A395,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="396">
-      <c r="B396" s="3" t="n"/>
-      <c r="D396" s="5">
-        <f>IF(A396="","",IFERROR(VLOOKUP(A396,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="397">
-      <c r="B397" s="3" t="n"/>
-      <c r="D397" s="5">
-        <f>IF(A397="","",IFERROR(VLOOKUP(A397,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="398">
-      <c r="B398" s="3" t="n"/>
-      <c r="D398" s="5">
-        <f>IF(A398="","",IFERROR(VLOOKUP(A398,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="399">
-      <c r="B399" s="3" t="n"/>
-      <c r="D399" s="5">
-        <f>IF(A399="","",IFERROR(VLOOKUP(A399,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="400">
-      <c r="B400" s="3" t="n"/>
-      <c r="D400" s="5">
-        <f>IF(A400="","",IFERROR(VLOOKUP(A400,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="401">
-      <c r="B401" s="3" t="n"/>
-      <c r="D401" s="5">
-        <f>IF(A401="","",IFERROR(VLOOKUP(A401,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="402">
-      <c r="B402" s="3" t="n"/>
-      <c r="D402" s="5">
-        <f>IF(A402="","",IFERROR(VLOOKUP(A402,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="403">
-      <c r="B403" s="3" t="n"/>
-      <c r="D403" s="5">
-        <f>IF(A403="","",IFERROR(VLOOKUP(A403,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="404">
-      <c r="B404" s="3" t="n"/>
-      <c r="D404" s="5">
-        <f>IF(A404="","",IFERROR(VLOOKUP(A404,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="405">
-      <c r="B405" s="3" t="n"/>
-      <c r="D405" s="5">
-        <f>IF(A405="","",IFERROR(VLOOKUP(A405,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="406">
-      <c r="B406" s="3" t="n"/>
-      <c r="D406" s="5">
-        <f>IF(A406="","",IFERROR(VLOOKUP(A406,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="407">
-      <c r="B407" s="3" t="n"/>
-      <c r="D407" s="5">
-        <f>IF(A407="","",IFERROR(VLOOKUP(A407,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="408">
-      <c r="B408" s="3" t="n"/>
-      <c r="D408" s="5">
-        <f>IF(A408="","",IFERROR(VLOOKUP(A408,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="409">
-      <c r="B409" s="3" t="n"/>
-      <c r="D409" s="5">
-        <f>IF(A409="","",IFERROR(VLOOKUP(A409,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="410">
-      <c r="B410" s="3" t="n"/>
-      <c r="D410" s="5">
-        <f>IF(A410="","",IFERROR(VLOOKUP(A410,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="411">
-      <c r="B411" s="3" t="n"/>
-      <c r="D411" s="5">
-        <f>IF(A411="","",IFERROR(VLOOKUP(A411,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="412">
-      <c r="B412" s="3" t="n"/>
-      <c r="D412" s="5">
-        <f>IF(A412="","",IFERROR(VLOOKUP(A412,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="413">
-      <c r="B413" s="3" t="n"/>
-      <c r="D413" s="5">
-        <f>IF(A413="","",IFERROR(VLOOKUP(A413,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="414">
-      <c r="B414" s="3" t="n"/>
-      <c r="D414" s="5">
-        <f>IF(A414="","",IFERROR(VLOOKUP(A414,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="415">
-      <c r="B415" s="3" t="n"/>
-      <c r="D415" s="5">
-        <f>IF(A415="","",IFERROR(VLOOKUP(A415,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="416">
-      <c r="B416" s="3" t="n"/>
-      <c r="D416" s="5">
-        <f>IF(A416="","",IFERROR(VLOOKUP(A416,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="417">
-      <c r="B417" s="3" t="n"/>
-      <c r="D417" s="5">
-        <f>IF(A417="","",IFERROR(VLOOKUP(A417,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="418">
-      <c r="B418" s="3" t="n"/>
-      <c r="D418" s="5">
-        <f>IF(A418="","",IFERROR(VLOOKUP(A418,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="419">
-      <c r="B419" s="3" t="n"/>
-      <c r="D419" s="5">
-        <f>IF(A419="","",IFERROR(VLOOKUP(A419,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="420">
-      <c r="B420" s="3" t="n"/>
-      <c r="D420" s="5">
-        <f>IF(A420="","",IFERROR(VLOOKUP(A420,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="421">
-      <c r="B421" s="3" t="n"/>
-      <c r="D421" s="5">
-        <f>IF(A421="","",IFERROR(VLOOKUP(A421,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="422">
-      <c r="B422" s="3" t="n"/>
-      <c r="D422" s="5">
-        <f>IF(A422="","",IFERROR(VLOOKUP(A422,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="423">
-      <c r="B423" s="3" t="n"/>
-      <c r="D423" s="5">
-        <f>IF(A423="","",IFERROR(VLOOKUP(A423,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="424">
-      <c r="B424" s="3" t="n"/>
-      <c r="D424" s="5">
-        <f>IF(A424="","",IFERROR(VLOOKUP(A424,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="425">
-      <c r="B425" s="3" t="n"/>
-      <c r="D425" s="5">
-        <f>IF(A425="","",IFERROR(VLOOKUP(A425,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="426">
-      <c r="B426" s="3" t="n"/>
-      <c r="D426" s="5">
-        <f>IF(A426="","",IFERROR(VLOOKUP(A426,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="427">
-      <c r="B427" s="3" t="n"/>
-      <c r="D427" s="5">
-        <f>IF(A427="","",IFERROR(VLOOKUP(A427,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="428">
-      <c r="B428" s="3" t="n"/>
-      <c r="D428" s="5">
-        <f>IF(A428="","",IFERROR(VLOOKUP(A428,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="429">
-      <c r="B429" s="3" t="n"/>
-      <c r="D429" s="5">
-        <f>IF(A429="","",IFERROR(VLOOKUP(A429,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="430">
-      <c r="B430" s="3" t="n"/>
-      <c r="D430" s="5">
-        <f>IF(A430="","",IFERROR(VLOOKUP(A430,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="431">
-      <c r="B431" s="3" t="n"/>
-      <c r="D431" s="5">
-        <f>IF(A431="","",IFERROR(VLOOKUP(A431,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="432">
-      <c r="B432" s="3" t="n"/>
-      <c r="D432" s="5">
-        <f>IF(A432="","",IFERROR(VLOOKUP(A432,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="433">
-      <c r="B433" s="3" t="n"/>
-      <c r="D433" s="5">
-        <f>IF(A433="","",IFERROR(VLOOKUP(A433,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="434">
-      <c r="B434" s="3" t="n"/>
-      <c r="D434" s="5">
-        <f>IF(A434="","",IFERROR(VLOOKUP(A434,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="435">
-      <c r="B435" s="3" t="n"/>
-      <c r="D435" s="5">
-        <f>IF(A435="","",IFERROR(VLOOKUP(A435,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="436">
-      <c r="B436" s="3" t="n"/>
-      <c r="D436" s="5">
-        <f>IF(A436="","",IFERROR(VLOOKUP(A436,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="437">
-      <c r="B437" s="3" t="n"/>
-      <c r="D437" s="5">
-        <f>IF(A437="","",IFERROR(VLOOKUP(A437,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="438">
-      <c r="B438" s="3" t="n"/>
-      <c r="D438" s="5">
-        <f>IF(A438="","",IFERROR(VLOOKUP(A438,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="439">
-      <c r="B439" s="3" t="n"/>
-      <c r="D439" s="5">
-        <f>IF(A439="","",IFERROR(VLOOKUP(A439,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="440">
-      <c r="B440" s="3" t="n"/>
-      <c r="D440" s="5">
-        <f>IF(A440="","",IFERROR(VLOOKUP(A440,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="441">
-      <c r="B441" s="3" t="n"/>
-      <c r="D441" s="5">
-        <f>IF(A441="","",IFERROR(VLOOKUP(A441,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="442">
-      <c r="B442" s="3" t="n"/>
-      <c r="D442" s="5">
-        <f>IF(A442="","",IFERROR(VLOOKUP(A442,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="443">
-      <c r="B443" s="3" t="n"/>
-      <c r="D443" s="5">
-        <f>IF(A443="","",IFERROR(VLOOKUP(A443,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="444">
-      <c r="B444" s="3" t="n"/>
-      <c r="D444" s="5">
-        <f>IF(A444="","",IFERROR(VLOOKUP(A444,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="445">
-      <c r="B445" s="3" t="n"/>
-      <c r="D445" s="5">
-        <f>IF(A445="","",IFERROR(VLOOKUP(A445,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="446">
-      <c r="B446" s="3" t="n"/>
-      <c r="D446" s="5">
-        <f>IF(A446="","",IFERROR(VLOOKUP(A446,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="447">
-      <c r="B447" s="3" t="n"/>
-      <c r="D447" s="5">
-        <f>IF(A447="","",IFERROR(VLOOKUP(A447,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="448">
-      <c r="B448" s="3" t="n"/>
-      <c r="D448" s="5">
-        <f>IF(A448="","",IFERROR(VLOOKUP(A448,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="449">
-      <c r="B449" s="3" t="n"/>
-      <c r="D449" s="5">
-        <f>IF(A449="","",IFERROR(VLOOKUP(A449,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="450">
-      <c r="B450" s="3" t="n"/>
-      <c r="D450" s="5">
-        <f>IF(A450="","",IFERROR(VLOOKUP(A450,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="451">
-      <c r="B451" s="3" t="n"/>
-      <c r="D451" s="5">
-        <f>IF(A451="","",IFERROR(VLOOKUP(A451,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="452">
-      <c r="B452" s="3" t="n"/>
-      <c r="D452" s="5">
-        <f>IF(A452="","",IFERROR(VLOOKUP(A452,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="453">
-      <c r="B453" s="3" t="n"/>
-      <c r="D453" s="5">
-        <f>IF(A453="","",IFERROR(VLOOKUP(A453,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="454">
-      <c r="B454" s="3" t="n"/>
-      <c r="D454" s="5">
-        <f>IF(A454="","",IFERROR(VLOOKUP(A454,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="455">
-      <c r="B455" s="3" t="n"/>
-      <c r="D455" s="5">
-        <f>IF(A455="","",IFERROR(VLOOKUP(A455,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="456">
-      <c r="B456" s="3" t="n"/>
-      <c r="D456" s="5">
-        <f>IF(A456="","",IFERROR(VLOOKUP(A456,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="457">
-      <c r="B457" s="3" t="n"/>
-      <c r="D457" s="5">
-        <f>IF(A457="","",IFERROR(VLOOKUP(A457,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="458">
-      <c r="B458" s="3" t="n"/>
-      <c r="D458" s="5">
-        <f>IF(A458="","",IFERROR(VLOOKUP(A458,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="459">
-      <c r="B459" s="3" t="n"/>
-      <c r="D459" s="5">
-        <f>IF(A459="","",IFERROR(VLOOKUP(A459,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="460">
-      <c r="B460" s="3" t="n"/>
-      <c r="D460" s="5">
-        <f>IF(A460="","",IFERROR(VLOOKUP(A460,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="461">
-      <c r="B461" s="3" t="n"/>
-      <c r="D461" s="5">
-        <f>IF(A461="","",IFERROR(VLOOKUP(A461,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="462">
-      <c r="B462" s="3" t="n"/>
-      <c r="D462" s="5">
-        <f>IF(A462="","",IFERROR(VLOOKUP(A462,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="463">
-      <c r="B463" s="3" t="n"/>
-      <c r="D463" s="5">
-        <f>IF(A463="","",IFERROR(VLOOKUP(A463,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="464">
-      <c r="B464" s="3" t="n"/>
-      <c r="D464" s="5">
-        <f>IF(A464="","",IFERROR(VLOOKUP(A464,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="465">
-      <c r="B465" s="3" t="n"/>
-      <c r="D465" s="5">
-        <f>IF(A465="","",IFERROR(VLOOKUP(A465,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="466">
-      <c r="B466" s="3" t="n"/>
-      <c r="D466" s="5">
-        <f>IF(A466="","",IFERROR(VLOOKUP(A466,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="467">
-      <c r="B467" s="3" t="n"/>
-      <c r="D467" s="5">
-        <f>IF(A467="","",IFERROR(VLOOKUP(A467,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="468">
-      <c r="B468" s="3" t="n"/>
-      <c r="D468" s="5">
-        <f>IF(A468="","",IFERROR(VLOOKUP(A468,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="469">
-      <c r="B469" s="3" t="n"/>
-      <c r="D469" s="5">
-        <f>IF(A469="","",IFERROR(VLOOKUP(A469,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="470">
-      <c r="B470" s="3" t="n"/>
-      <c r="D470" s="5">
-        <f>IF(A470="","",IFERROR(VLOOKUP(A470,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="471">
-      <c r="B471" s="3" t="n"/>
-      <c r="D471" s="5">
-        <f>IF(A471="","",IFERROR(VLOOKUP(A471,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="472">
-      <c r="B472" s="3" t="n"/>
-      <c r="D472" s="5">
-        <f>IF(A472="","",IFERROR(VLOOKUP(A472,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="473">
-      <c r="B473" s="3" t="n"/>
-      <c r="D473" s="5">
-        <f>IF(A473="","",IFERROR(VLOOKUP(A473,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="474">
-      <c r="B474" s="3" t="n"/>
-      <c r="D474" s="5">
-        <f>IF(A474="","",IFERROR(VLOOKUP(A474,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="475">
-      <c r="B475" s="3" t="n"/>
-      <c r="D475" s="5">
-        <f>IF(A475="","",IFERROR(VLOOKUP(A475,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="476">
-      <c r="B476" s="3" t="n"/>
-      <c r="D476" s="5">
-        <f>IF(A476="","",IFERROR(VLOOKUP(A476,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="477">
-      <c r="B477" s="3" t="n"/>
-      <c r="D477" s="5">
-        <f>IF(A477="","",IFERROR(VLOOKUP(A477,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="478">
-      <c r="B478" s="3" t="n"/>
-      <c r="D478" s="5">
-        <f>IF(A478="","",IFERROR(VLOOKUP(A478,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="479">
-      <c r="B479" s="3" t="n"/>
-      <c r="D479" s="5">
-        <f>IF(A479="","",IFERROR(VLOOKUP(A479,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="480">
-      <c r="B480" s="3" t="n"/>
-      <c r="D480" s="5">
-        <f>IF(A480="","",IFERROR(VLOOKUP(A480,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="481">
-      <c r="B481" s="3" t="n"/>
-      <c r="D481" s="5">
-        <f>IF(A481="","",IFERROR(VLOOKUP(A481,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="482">
-      <c r="B482" s="3" t="n"/>
-      <c r="D482" s="5">
-        <f>IF(A482="","",IFERROR(VLOOKUP(A482,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="483">
-      <c r="B483" s="3" t="n"/>
-      <c r="D483" s="5">
-        <f>IF(A483="","",IFERROR(VLOOKUP(A483,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="484">
-      <c r="B484" s="3" t="n"/>
-      <c r="D484" s="5">
-        <f>IF(A484="","",IFERROR(VLOOKUP(A484,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="485">
-      <c r="B485" s="3" t="n"/>
-      <c r="D485" s="5">
-        <f>IF(A485="","",IFERROR(VLOOKUP(A485,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="486">
-      <c r="B486" s="3" t="n"/>
-      <c r="D486" s="5">
-        <f>IF(A486="","",IFERROR(VLOOKUP(A486,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="487">
-      <c r="B487" s="3" t="n"/>
-      <c r="D487" s="5">
-        <f>IF(A487="","",IFERROR(VLOOKUP(A487,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="488">
-      <c r="B488" s="3" t="n"/>
-      <c r="D488" s="5">
-        <f>IF(A488="","",IFERROR(VLOOKUP(A488,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="489">
-      <c r="B489" s="3" t="n"/>
-      <c r="D489" s="5">
-        <f>IF(A489="","",IFERROR(VLOOKUP(A489,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="490">
-      <c r="B490" s="3" t="n"/>
-      <c r="D490" s="5">
-        <f>IF(A490="","",IFERROR(VLOOKUP(A490,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="491">
-      <c r="B491" s="3" t="n"/>
-      <c r="D491" s="5">
-        <f>IF(A491="","",IFERROR(VLOOKUP(A491,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="492">
-      <c r="B492" s="3" t="n"/>
-      <c r="D492" s="5">
-        <f>IF(A492="","",IFERROR(VLOOKUP(A492,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="493">
-      <c r="B493" s="3" t="n"/>
-      <c r="D493" s="5">
-        <f>IF(A493="","",IFERROR(VLOOKUP(A493,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="494">
-      <c r="B494" s="3" t="n"/>
-      <c r="D494" s="5">
-        <f>IF(A494="","",IFERROR(VLOOKUP(A494,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="495">
-      <c r="B495" s="3" t="n"/>
-      <c r="D495" s="5">
-        <f>IF(A495="","",IFERROR(VLOOKUP(A495,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="496">
-      <c r="B496" s="3" t="n"/>
-      <c r="D496" s="5">
-        <f>IF(A496="","",IFERROR(VLOOKUP(A496,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="497">
-      <c r="B497" s="3" t="n"/>
-      <c r="D497" s="5">
-        <f>IF(A497="","",IFERROR(VLOOKUP(A497,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="498">
-      <c r="B498" s="3" t="n"/>
-      <c r="D498" s="5">
-        <f>IF(A498="","",IFERROR(VLOOKUP(A498,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="499">
-      <c r="B499" s="3" t="n"/>
-      <c r="D499" s="5">
-        <f>IF(A499="","",IFERROR(VLOOKUP(A499,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="500">
-      <c r="B500" s="3" t="n"/>
-      <c r="D500" s="5">
-        <f>IF(A500="","",IFERROR(VLOOKUP(A500,Номера!$A$2:$E$500,5,FALSE),"нет такого ID"))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Номера!$A$2:$A$500</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -165,11 +165,31 @@
         <t>Ссылка на запись всего концерта в VK, например https://vk.com/video-123_456. Если видео закрытое, вставьте адрес из кода для вставки (video_ext.php?...hash=...).</t>
       </text>
     </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Постоянный адрес концерта на сайте. Появляется сам, потом не меняйте.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Каталог</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Постоянный адрес направления на сайте. Появляется сам, потом не меняйте.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Каталог</author>
@@ -219,7 +239,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Каталог</author>
@@ -228,6 +248,11 @@
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>Так же, как в листе «Номера». Лист нужен только если у человека есть описание или ссылка.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Постоянный адрес страницы человека. Появляется сам, потом не меняйте: к нему привязан аккаунт постановщика.</t>
       </text>
     </comment>
   </commentList>
@@ -523,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -597,46 +622,77 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Столбец «ID» в листах «Концерты», «Направления» и «Люди» — постоянный адрес. Он появляется сам (меню Каталог → Проставить ID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>и после публикации не меняется, даже если вы переименуете концерт, направление или человека.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Переименовывать лучше через меню: выделите ячейку с названием или именем и выберите Каталог → Переименовать.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Меню само поправит все упоминания в листе «Номера».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Время вводите так: ч:мм:сс, например 0:20:52. Столбцы «Начало» и «Конец» в формате «простой текст»,</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>не меняйте формат: иначе Google превратит 20:52 в 20 часов 52 минуты.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Не переименовывайте листы и не меняйте заголовки в первой строке.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>ID номера — короткий код из латинских букв, цифр, дефиса: он станет частью адреса страницы.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>После того как номер опубликован, ID лучше не менять: сменится адрес страницы.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Если в таблице ошибка, сайт не обновится, а в отчёте сборки будет написано, на каком листе и в какой строке.</t>
         </is>
@@ -653,13 +709,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:E500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="54" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -683,6 +740,11 @@
           <t>Описание</t>
         </is>
       </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" s="3" t="n"/>
@@ -2692,11 +2754,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2710,9 +2773,15 @@
           <t>Описание</t>
         </is>
       </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -5821,12 +5890,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -5845,6 +5915,11 @@
           <t>Ссылка</t>
         </is>
       </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -202,7 +202,7 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Порядок выступления. Если не заполнить, пойдёт в порядке строк.</t>
+        <t>Необязательно. Если пусто, номера идут по времени начала.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3. Лист «Номера»: по строке на номер. «Концерт» и «Направление» выбираются из списка.</t>
+          <t>3. Лист «Номера»: по строке на номер. «Концерт» и «Направление» выбираются из списка. «№ в концерте» не нужен: номера идут по времени начала.</t>
         </is>
       </c>
     </row>
